--- a/examples/nikita_table1.xlsx
+++ b/examples/nikita_table1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rt\Work\Tristan\tristan_tools\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40C5FAB0-BB0C-4347-937B-0A4F07D6E9D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C503D11-3022-47E8-8F27-A3CF41F7FD84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="5325" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Date</t>
   </si>
@@ -51,30 +51,12 @@
     <t>CPC</t>
   </si>
   <si>
-    <t>SL</t>
-  </si>
-  <si>
-    <t>CPSL</t>
-  </si>
-  <si>
     <t>CPFD</t>
   </si>
   <si>
     <t>CR</t>
   </si>
   <si>
-    <t>Acom</t>
-  </si>
-  <si>
-    <t>FD Comm</t>
-  </si>
-  <si>
-    <t>UPS Comm</t>
-  </si>
-  <si>
-    <t>Q FD</t>
-  </si>
-  <si>
     <t>Sub Declined</t>
   </si>
   <si>
@@ -82,6 +64,21 @@
   </si>
   <si>
     <t>Заголовок месяца</t>
+  </si>
+  <si>
+    <t>FTD Count</t>
+  </si>
+  <si>
+    <t>FTD Sum</t>
+  </si>
+  <si>
+    <t>Redep Count</t>
+  </si>
+  <si>
+    <t>Redep Sum</t>
+  </si>
+  <si>
+    <t>Avg Dep</t>
   </si>
 </sst>
 </file>
@@ -153,7 +150,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -177,37 +174,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -217,9 +183,7 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -232,22 +196,38 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -256,7 +236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -273,49 +253,52 @@
     <xf numFmtId="10" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -598,155 +581,155 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="3" customWidth="1"/>
     <col min="3" max="3" width="14.42578125" style="4" customWidth="1"/>
     <col min="4" max="4" width="17.85546875" style="4" customWidth="1"/>
-    <col min="5" max="5" width="9.42578125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" style="6" customWidth="1"/>
     <col min="6" max="6" width="14.42578125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" style="7" customWidth="1"/>
-    <col min="8" max="8" width="9.5703125" style="7" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" style="6" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" style="6" customWidth="1"/>
     <col min="9" max="9" width="13.28515625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="10" style="7" customWidth="1"/>
-    <col min="11" max="11" width="10" style="4" customWidth="1"/>
-    <col min="12" max="12" width="10" style="7" customWidth="1"/>
-    <col min="13" max="13" width="16" style="4" customWidth="1"/>
-    <col min="14" max="14" width="15" style="5" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="2" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="6" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="8" customWidth="1"/>
-    <col min="18" max="19" width="14.42578125" style="6" customWidth="1"/>
+    <col min="10" max="10" width="10" style="6" customWidth="1"/>
+    <col min="11" max="11" width="16" style="4" customWidth="1"/>
+    <col min="12" max="12" width="15" style="5" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="16" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="7" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="16" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="20" customWidth="1"/>
+    <col min="18" max="18" width="14.140625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="8"/>
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="12" t="s">
+      <c r="N1" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="12" t="s">
+      <c r="R1" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="P1" s="15" t="s">
+    </row>
+    <row r="2" spans="1:18" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="R1" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="S1" s="17" t="s">
-        <v>15</v>
-      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="18"/>
+      <c r="P2" s="18"/>
+      <c r="Q2" s="18"/>
+      <c r="R2" s="18"/>
     </row>
-    <row r="2" spans="1:19" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="19"/>
-      <c r="N2" s="19"/>
-      <c r="O2" s="19"/>
-      <c r="P2" s="19"/>
-      <c r="Q2" s="19"/>
-      <c r="R2" s="19"/>
-      <c r="S2" s="20"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C3" s="4">
         <v>11.11</v>
       </c>
       <c r="D3" s="4">
         <v>11.11</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="6">
         <v>11</v>
       </c>
       <c r="F3" s="4">
         <v>11</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="6">
         <v>11</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="6">
         <v>11</v>
       </c>
       <c r="I3" s="4">
         <v>11</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="6">
         <v>11</v>
       </c>
       <c r="K3" s="4">
         <v>11</v>
       </c>
-      <c r="L3" s="7">
-        <v>11</v>
-      </c>
-      <c r="M3" s="4">
-        <v>11</v>
-      </c>
-      <c r="N3" s="5">
+      <c r="L3" s="5">
         <v>0.11</v>
       </c>
-      <c r="Q3" s="8">
+      <c r="N3" s="16">
+        <v>12</v>
+      </c>
+      <c r="O3" s="7">
         <v>11.11</v>
+      </c>
+      <c r="P3" s="16">
+        <v>34</v>
+      </c>
+      <c r="Q3" s="20">
+        <v>11.11</v>
+      </c>
+      <c r="R3" s="7">
+        <v>12.34</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A2:R2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/examples/nikita_table1.xlsx
+++ b/examples/nikita_table1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rt\Work\Tristan\tristan_tools\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C503D11-3022-47E8-8F27-A3CF41F7FD84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A84FA779-E138-46D3-98B3-71D36D71AF4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -286,19 +286,19 @@
     <xf numFmtId="1" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -600,7 +600,7 @@
     <col min="14" max="14" width="14.42578125" style="16" customWidth="1"/>
     <col min="15" max="15" width="14.42578125" style="7" customWidth="1"/>
     <col min="16" max="16" width="14.42578125" style="16" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="20" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="18" customWidth="1"/>
     <col min="18" max="18" width="14.140625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
@@ -651,34 +651,34 @@
       <c r="P1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="19" t="s">
+      <c r="Q1" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="21" t="s">
+      <c r="R1" s="19" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18"/>
-      <c r="O2" s="18"/>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="18"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21"/>
+      <c r="O2" s="21"/>
+      <c r="P2" s="21"/>
+      <c r="Q2" s="21"/>
+      <c r="R2" s="21"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C3" s="4">
@@ -720,7 +720,7 @@
       <c r="P3" s="16">
         <v>34</v>
       </c>
-      <c r="Q3" s="20">
+      <c r="Q3" s="18">
         <v>11.11</v>
       </c>
       <c r="R3" s="7">
